--- a/bookdata/roadbook_sample.xlsx
+++ b/bookdata/roadbook_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imamuu/Documents/project/rally_印刷関連/common/roadbookMaker/prod/bookdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imamuu/Documents/project/rally_印刷関連/roadbookMaker/prod/bookdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369E8C52-7645-644C-89C0-7B671F2484C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D009AACC-BF7E-8044-8B95-D81371B11EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{219DE134-4725-C842-B216-6F156E98A0A3}"/>
+    <workbookView xWindow="4480" yWindow="1300" windowWidth="29400" windowHeight="18360" activeTab="2" xr2:uid="{219DE134-4725-C842-B216-6F156E98A0A3}"/>
   </bookViews>
   <sheets>
     <sheet name="LEG　１" sheetId="1" r:id="rId1"/>
@@ -1117,10 +1117,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>,,,,,,,,,,map</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>京都府丹後文化会館駐車場</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -1156,6 +1152,10 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>,,,,,,,,map</t>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
@@ -1167,12 +1167,12 @@
     <numFmt numFmtId="178" formatCode="0.00_ "/>
     <numFmt numFmtId="179" formatCode="[mm]&quot;’&quot;"/>
     <numFmt numFmtId="180" formatCode="0.00&quot;km&quot;"/>
-    <numFmt numFmtId="182" formatCode="0.00_);\(0.00\)"/>
-    <numFmt numFmtId="183" formatCode="h:mm;@"/>
-    <numFmt numFmtId="184" formatCode="0.0_ "/>
-    <numFmt numFmtId="185" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="187" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="181" formatCode="0.00_);\(0.00\)"/>
+    <numFmt numFmtId="182" formatCode="h:mm;@"/>
+    <numFmt numFmtId="183" formatCode="0.0_ "/>
+    <numFmt numFmtId="184" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="185" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -1240,7 +1240,6 @@
     <font>
       <sz val="12"/>
       <name val="System"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1525,7 +1524,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1542,7 +1541,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1569,17 +1568,17 @@
     <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="185" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
@@ -1597,10 +1596,10 @@
     <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
@@ -1621,16 +1620,16 @@
     <xf numFmtId="176" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1648,7 +1647,7 @@
     <xf numFmtId="178" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1657,7 +1656,7 @@
     <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1666,7 +1665,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" readingOrder="1"/>
     </xf>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1675,7 +1674,7 @@
     <xf numFmtId="180" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="18" fillId="2" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1687,10 +1686,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1699,13 +1698,13 @@
     <xf numFmtId="178" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="184" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="185" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="186" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1730,11 +1729,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="184" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="183" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1746,48 +1745,6 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -21439,7 +21396,7 @@
         <v>14</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1">
@@ -21665,10 +21622,10 @@
     <row r="11" spans="1:16" ht="14.25" customHeight="1" thickBot="1">
       <c r="A11" s="77"/>
       <c r="B11" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D11" s="41" t="s">
         <v>0</v>
@@ -23332,12 +23289,12 @@
     </row>
     <row r="68" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A68" s="12"/>
-      <c r="B68" s="86"/>
-      <c r="C68" s="86"/>
-      <c r="D68" s="87"/>
-      <c r="E68" s="88"/>
-      <c r="F68" s="87"/>
-      <c r="G68" s="89"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="13"/>
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="12"/>
@@ -23346,12 +23303,12 @@
     </row>
     <row r="69" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A69" s="12"/>
-      <c r="B69" s="86"/>
-      <c r="C69" s="86"/>
-      <c r="D69" s="87"/>
-      <c r="E69" s="88"/>
-      <c r="F69" s="87"/>
-      <c r="G69" s="89"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="13"/>
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="12"/>
@@ -23360,12 +23317,12 @@
     </row>
     <row r="70" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A70" s="12"/>
-      <c r="B70" s="86"/>
-      <c r="C70" s="86"/>
-      <c r="D70" s="87"/>
-      <c r="E70" s="88"/>
-      <c r="F70" s="87"/>
-      <c r="G70" s="89"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
       <c r="J70" s="12"/>
@@ -23374,12 +23331,12 @@
     </row>
     <row r="71" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A71" s="12"/>
-      <c r="B71" s="86"/>
-      <c r="C71" s="86"/>
-      <c r="D71" s="87"/>
-      <c r="E71" s="88"/>
-      <c r="F71" s="87"/>
-      <c r="G71" s="89"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="12"/>
@@ -23388,12 +23345,12 @@
     </row>
     <row r="72" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A72" s="12"/>
-      <c r="B72" s="86"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="87"/>
-      <c r="E72" s="88"/>
-      <c r="F72" s="87"/>
-      <c r="G72" s="89"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="13"/>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
       <c r="J72" s="12"/>
@@ -23402,12 +23359,12 @@
     </row>
     <row r="73" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A73" s="12"/>
-      <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="90"/>
-      <c r="E73" s="91"/>
-      <c r="F73" s="90"/>
-      <c r="G73" s="89"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="13"/>
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
       <c r="J73" s="12"/>
@@ -23416,12 +23373,12 @@
     </row>
     <row r="74" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A74" s="12"/>
-      <c r="B74" s="86"/>
-      <c r="C74" s="86"/>
-      <c r="D74" s="87"/>
-      <c r="E74" s="88"/>
-      <c r="F74" s="87"/>
-      <c r="G74" s="92"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="16"/>
       <c r="H74" s="16"/>
       <c r="I74" s="16"/>
       <c r="J74" s="12"/>
@@ -23430,12 +23387,12 @@
     </row>
     <row r="75" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A75" s="12"/>
-      <c r="B75" s="86"/>
-      <c r="C75" s="86"/>
-      <c r="D75" s="87"/>
-      <c r="E75" s="88"/>
-      <c r="F75" s="87"/>
-      <c r="G75" s="92"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="16"/>
       <c r="H75" s="16"/>
       <c r="I75" s="13"/>
       <c r="J75" s="12"/>
@@ -23444,12 +23401,12 @@
     </row>
     <row r="76" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A76" s="12"/>
-      <c r="B76" s="86"/>
-      <c r="C76" s="86"/>
-      <c r="D76" s="87"/>
-      <c r="E76" s="88"/>
-      <c r="F76" s="87"/>
-      <c r="G76" s="92"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="16"/>
       <c r="H76" s="16"/>
       <c r="I76" s="13"/>
       <c r="J76" s="12"/>
@@ -23458,12 +23415,12 @@
     </row>
     <row r="77" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A77" s="12"/>
-      <c r="B77" s="86"/>
-      <c r="C77" s="86"/>
-      <c r="D77" s="87"/>
-      <c r="E77" s="88"/>
-      <c r="F77" s="87"/>
-      <c r="G77" s="92"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="16"/>
       <c r="H77" s="16"/>
       <c r="I77" s="13"/>
       <c r="J77" s="12"/>
@@ -23472,12 +23429,12 @@
     </row>
     <row r="78" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A78" s="12"/>
-      <c r="B78" s="86"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="87"/>
-      <c r="E78" s="88"/>
-      <c r="F78" s="87"/>
-      <c r="G78" s="89"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="13"/>
       <c r="H78" s="13"/>
       <c r="I78" s="13"/>
       <c r="J78" s="12"/>
@@ -23486,12 +23443,12 @@
     </row>
     <row r="79" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A79" s="12"/>
-      <c r="B79" s="86"/>
-      <c r="C79" s="86"/>
-      <c r="D79" s="87"/>
-      <c r="E79" s="88"/>
-      <c r="F79" s="87"/>
-      <c r="G79" s="89"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="13"/>
       <c r="H79" s="13"/>
       <c r="I79" s="13"/>
       <c r="J79" s="12"/>
@@ -23500,12 +23457,12 @@
     </row>
     <row r="80" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A80" s="12"/>
-      <c r="B80" s="86"/>
-      <c r="C80" s="86"/>
-      <c r="D80" s="87"/>
-      <c r="E80" s="88"/>
-      <c r="F80" s="87"/>
-      <c r="G80" s="89"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="13"/>
       <c r="H80" s="13"/>
       <c r="I80" s="13"/>
       <c r="J80" s="12"/>
@@ -23514,12 +23471,12 @@
     </row>
     <row r="81" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A81" s="12"/>
-      <c r="B81" s="86"/>
-      <c r="C81" s="86"/>
-      <c r="D81" s="87"/>
-      <c r="E81" s="88"/>
-      <c r="F81" s="87"/>
-      <c r="G81" s="89"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="13"/>
       <c r="H81" s="13"/>
       <c r="I81" s="13"/>
       <c r="J81" s="12"/>
@@ -23528,12 +23485,12 @@
     </row>
     <row r="82" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A82" s="12"/>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="87"/>
-      <c r="E82" s="88"/>
-      <c r="F82" s="87"/>
-      <c r="G82" s="89"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="13"/>
       <c r="H82" s="13"/>
       <c r="I82" s="13"/>
       <c r="J82" s="12"/>
@@ -23542,12 +23499,12 @@
     </row>
     <row r="83" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A83" s="12"/>
-      <c r="B83" s="86"/>
-      <c r="C83" s="86"/>
-      <c r="D83" s="87"/>
-      <c r="E83" s="88"/>
-      <c r="F83" s="87"/>
-      <c r="G83" s="89"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="13"/>
       <c r="H83" s="13"/>
       <c r="I83" s="13"/>
       <c r="J83" s="12"/>
@@ -23556,12 +23513,12 @@
     </row>
     <row r="84" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A84" s="12"/>
-      <c r="B84" s="86"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="90"/>
-      <c r="E84" s="91"/>
-      <c r="F84" s="90"/>
-      <c r="G84" s="89"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="58"/>
+      <c r="E84" s="59"/>
+      <c r="F84" s="58"/>
+      <c r="G84" s="13"/>
       <c r="H84" s="13"/>
       <c r="I84" s="13"/>
       <c r="J84" s="12"/>
@@ -23570,12 +23527,12 @@
     </row>
     <row r="85" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A85" s="12"/>
-      <c r="B85" s="86"/>
-      <c r="C85" s="86"/>
-      <c r="D85" s="87"/>
-      <c r="E85" s="88"/>
-      <c r="F85" s="87"/>
-      <c r="G85" s="92"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="16"/>
       <c r="H85" s="13"/>
       <c r="I85" s="13"/>
       <c r="J85" s="12"/>
@@ -23584,12 +23541,12 @@
     </row>
     <row r="86" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A86" s="12"/>
-      <c r="B86" s="86"/>
-      <c r="C86" s="86"/>
-      <c r="D86" s="87"/>
-      <c r="E86" s="88"/>
-      <c r="F86" s="87"/>
-      <c r="G86" s="92"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="16"/>
       <c r="H86" s="13"/>
       <c r="I86" s="13"/>
       <c r="J86" s="12"/>
@@ -23598,12 +23555,12 @@
     </row>
     <row r="87" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A87" s="12"/>
-      <c r="B87" s="86"/>
-      <c r="C87" s="86"/>
-      <c r="D87" s="87"/>
-      <c r="E87" s="88"/>
-      <c r="F87" s="87"/>
-      <c r="G87" s="92"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="16"/>
       <c r="H87" s="13"/>
       <c r="I87" s="13"/>
       <c r="J87" s="12"/>
@@ -23612,12 +23569,12 @@
     </row>
     <row r="88" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A88" s="19"/>
-      <c r="B88" s="86"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="87"/>
-      <c r="E88" s="88"/>
-      <c r="F88" s="87"/>
-      <c r="G88" s="92"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="16"/>
       <c r="H88" s="13"/>
       <c r="I88" s="13"/>
       <c r="J88" s="12"/>
@@ -23626,12 +23583,12 @@
     </row>
     <row r="89" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A89" s="19"/>
-      <c r="B89" s="86"/>
-      <c r="C89" s="86"/>
-      <c r="D89" s="87"/>
-      <c r="E89" s="88"/>
-      <c r="F89" s="87"/>
-      <c r="G89" s="92"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="16"/>
       <c r="H89" s="13"/>
       <c r="I89" s="13"/>
       <c r="J89" s="12"/>
@@ -23640,12 +23597,12 @@
     </row>
     <row r="90" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A90" s="19"/>
-      <c r="B90" s="86"/>
-      <c r="C90" s="86"/>
-      <c r="D90" s="87"/>
-      <c r="E90" s="88"/>
-      <c r="F90" s="87"/>
-      <c r="G90" s="92"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="16"/>
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
       <c r="J90" s="12"/>
@@ -23654,12 +23611,12 @@
     </row>
     <row r="91" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A91" s="12"/>
-      <c r="B91" s="86"/>
-      <c r="C91" s="86"/>
-      <c r="D91" s="87"/>
-      <c r="E91" s="88"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="92"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="16"/>
       <c r="H91" s="13"/>
       <c r="I91" s="13"/>
       <c r="J91" s="12"/>
@@ -23668,12 +23625,12 @@
     </row>
     <row r="92" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A92" s="12"/>
-      <c r="B92" s="86"/>
-      <c r="C92" s="86"/>
-      <c r="D92" s="87"/>
-      <c r="E92" s="88"/>
-      <c r="F92" s="87"/>
-      <c r="G92" s="89"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="13"/>
       <c r="H92" s="13"/>
       <c r="I92" s="13"/>
       <c r="J92" s="12"/>
@@ -23682,12 +23639,12 @@
     </row>
     <row r="93" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A93" s="12"/>
-      <c r="B93" s="86"/>
-      <c r="C93" s="86"/>
-      <c r="D93" s="87"/>
-      <c r="E93" s="88"/>
-      <c r="F93" s="87"/>
-      <c r="G93" s="89"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="13"/>
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
       <c r="J93" s="12"/>
@@ -24970,11 +24927,11 @@
     <row r="185" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
-      <c r="C185" s="79"/>
-      <c r="D185" s="80"/>
-      <c r="E185" s="80"/>
-      <c r="F185" s="80"/>
-      <c r="G185" s="81"/>
+      <c r="C185" s="12"/>
+      <c r="D185" s="56"/>
+      <c r="E185" s="56"/>
+      <c r="F185" s="56"/>
+      <c r="G185" s="13"/>
       <c r="H185" s="13"/>
       <c r="I185" s="13"/>
       <c r="J185" s="12"/>
@@ -24984,11 +24941,11 @@
     <row r="186" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
-      <c r="C186" s="79"/>
-      <c r="D186" s="80"/>
-      <c r="E186" s="80"/>
-      <c r="F186" s="82"/>
-      <c r="G186" s="81"/>
+      <c r="C186" s="12"/>
+      <c r="D186" s="56"/>
+      <c r="E186" s="56"/>
+      <c r="F186" s="17"/>
+      <c r="G186" s="13"/>
       <c r="H186" s="13"/>
       <c r="I186" s="13"/>
       <c r="J186" s="12"/>
@@ -24998,11 +24955,11 @@
     <row r="187" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
-      <c r="C187" s="79"/>
-      <c r="D187" s="83"/>
-      <c r="E187" s="83"/>
-      <c r="F187" s="83"/>
-      <c r="G187" s="81"/>
+      <c r="C187" s="12"/>
+      <c r="D187" s="60"/>
+      <c r="E187" s="60"/>
+      <c r="F187" s="60"/>
+      <c r="G187" s="13"/>
       <c r="H187" s="13"/>
       <c r="I187" s="13"/>
       <c r="J187" s="12"/>
@@ -25012,11 +24969,11 @@
     <row r="188" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
-      <c r="C188" s="79"/>
-      <c r="D188" s="80"/>
-      <c r="E188" s="84"/>
-      <c r="F188" s="80"/>
-      <c r="G188" s="81"/>
+      <c r="C188" s="12"/>
+      <c r="D188" s="56"/>
+      <c r="E188" s="15"/>
+      <c r="F188" s="56"/>
+      <c r="G188" s="13"/>
       <c r="H188" s="13"/>
       <c r="I188" s="13"/>
       <c r="J188" s="12"/>
@@ -25026,11 +24983,11 @@
     <row r="189" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
-      <c r="C189" s="79"/>
-      <c r="D189" s="80"/>
-      <c r="E189" s="84"/>
-      <c r="F189" s="80"/>
-      <c r="G189" s="81"/>
+      <c r="C189" s="12"/>
+      <c r="D189" s="56"/>
+      <c r="E189" s="15"/>
+      <c r="F189" s="56"/>
+      <c r="G189" s="13"/>
       <c r="H189" s="13"/>
       <c r="I189" s="13"/>
       <c r="J189" s="12"/>
@@ -25040,11 +24997,11 @@
     <row r="190" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
-      <c r="C190" s="79"/>
-      <c r="D190" s="85"/>
-      <c r="E190" s="80"/>
-      <c r="F190" s="80"/>
-      <c r="G190" s="81"/>
+      <c r="C190" s="12"/>
+      <c r="D190" s="14"/>
+      <c r="E190" s="56"/>
+      <c r="F190" s="56"/>
+      <c r="G190" s="13"/>
       <c r="H190" s="13"/>
       <c r="I190" s="13"/>
       <c r="J190" s="12"/>
@@ -25054,11 +25011,11 @@
     <row r="191" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
-      <c r="C191" s="79"/>
-      <c r="D191" s="85"/>
-      <c r="E191" s="84"/>
-      <c r="F191" s="80"/>
-      <c r="G191" s="81"/>
+      <c r="C191" s="12"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="15"/>
+      <c r="F191" s="56"/>
+      <c r="G191" s="13"/>
       <c r="H191" s="13"/>
       <c r="I191" s="13"/>
       <c r="J191" s="12"/>
@@ -25068,11 +25025,11 @@
     <row r="192" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
-      <c r="C192" s="79"/>
-      <c r="D192" s="85"/>
-      <c r="E192" s="84"/>
-      <c r="F192" s="80"/>
-      <c r="G192" s="81"/>
+      <c r="C192" s="12"/>
+      <c r="D192" s="14"/>
+      <c r="E192" s="15"/>
+      <c r="F192" s="56"/>
+      <c r="G192" s="13"/>
       <c r="H192" s="13"/>
       <c r="I192" s="13"/>
       <c r="J192" s="12"/>
@@ -25082,11 +25039,11 @@
     <row r="193" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
-      <c r="C193" s="79"/>
-      <c r="D193" s="85"/>
-      <c r="E193" s="84"/>
-      <c r="F193" s="80"/>
-      <c r="G193" s="81"/>
+      <c r="C193" s="12"/>
+      <c r="D193" s="14"/>
+      <c r="E193" s="15"/>
+      <c r="F193" s="56"/>
+      <c r="G193" s="13"/>
       <c r="H193" s="13"/>
       <c r="I193" s="13"/>
       <c r="J193" s="12"/>
@@ -25096,11 +25053,11 @@
     <row r="194" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
-      <c r="C194" s="79"/>
-      <c r="D194" s="82"/>
-      <c r="E194" s="82"/>
-      <c r="F194" s="82"/>
-      <c r="G194" s="81"/>
+      <c r="C194" s="12"/>
+      <c r="D194" s="17"/>
+      <c r="E194" s="17"/>
+      <c r="F194" s="17"/>
+      <c r="G194" s="13"/>
       <c r="H194" s="13"/>
       <c r="I194" s="13"/>
       <c r="J194" s="12"/>
@@ -25110,11 +25067,11 @@
     <row r="195" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
-      <c r="C195" s="79"/>
-      <c r="D195" s="82"/>
-      <c r="E195" s="82"/>
-      <c r="F195" s="82"/>
-      <c r="G195" s="81"/>
+      <c r="C195" s="12"/>
+      <c r="D195" s="17"/>
+      <c r="E195" s="17"/>
+      <c r="F195" s="17"/>
+      <c r="G195" s="13"/>
       <c r="H195" s="13"/>
       <c r="I195" s="13"/>
       <c r="J195" s="12"/>
@@ -25124,11 +25081,11 @@
     <row r="196" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
-      <c r="C196" s="79"/>
-      <c r="D196" s="82"/>
-      <c r="E196" s="80"/>
-      <c r="F196" s="80"/>
-      <c r="G196" s="81"/>
+      <c r="C196" s="12"/>
+      <c r="D196" s="17"/>
+      <c r="E196" s="56"/>
+      <c r="F196" s="56"/>
+      <c r="G196" s="13"/>
       <c r="H196" s="13"/>
       <c r="I196" s="13"/>
       <c r="J196" s="12"/>
@@ -25138,11 +25095,11 @@
     <row r="197" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
-      <c r="C197" s="79"/>
-      <c r="D197" s="82"/>
-      <c r="E197" s="80"/>
-      <c r="F197" s="80"/>
-      <c r="G197" s="81"/>
+      <c r="C197" s="12"/>
+      <c r="D197" s="17"/>
+      <c r="E197" s="56"/>
+      <c r="F197" s="56"/>
+      <c r="G197" s="13"/>
       <c r="H197" s="13"/>
       <c r="I197" s="13"/>
       <c r="J197" s="12"/>
@@ -25839,6 +25796,7 @@
     <col min="15" max="15" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8" style="69" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="10.83203125" style="69"/>
+    <col min="19" max="19" width="7.1640625" customWidth="1"/>
     <col min="20" max="20" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -25911,7 +25869,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -26485,7 +26443,7 @@
         <v>13.19</v>
       </c>
       <c r="K24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L24" t="s">
         <v>112</v>
@@ -26547,7 +26505,7 @@
         <v>13.19</v>
       </c>
       <c r="K25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L25" t="s">
         <v>112</v>
@@ -26901,7 +26859,7 @@
     </row>
     <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -26925,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
